--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="Rfcc9103d229c4ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R3a8702f4460d46f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H15"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-02 09:10:38（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C13,A5)</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIF(C8:C15,A5)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C13,D5)</x:f>
+        <x:f>COUNTIF(C8:C15,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C13,F5)</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIF(C8:C15,F5)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -544,149 +544,173 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="92" customHeight="1">
+    <x:row r="9" ht="109" customHeight="1">
       <x:c r="A9" s="7" t="str">
+        <x:v>CA-038</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="str">
+        <x:v>标准 Shipping 打包 GameFeatureData 规则错误</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="str">
+        <x:v>标准 BuildCookRun 编译和 cook 产品写出后，因 AssetManager 缺少 GameFeatureData 规则失败，UAT 退出 25。诊断包使用 skipbuild/skipcook 完成打包，不代表该配置错误已解决。</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="str">
+        <x:v>确认规则修复范围；当前聊天授权测试与方案，未实施修复。标准发布复验另见 CA-038.02。</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="str">
+        <x:v>Shipping 报告构建错误与 build_metadata exit_code=25</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="str"/>
+    </x:row>
+    <x:row r="10" ht="92" customHeight="1">
+      <x:c r="A10" s="7" t="str">
         <x:v>CA-011</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>教室门蓝图运行时挂接与转轴逻辑</x:v>
-      </x:c>
-      <x:c r="C9" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="str">
-        <x:v>门零件在编辑器挂到根组件，BeginPlay 以 KeepWorld 快照挂到 DoorPivot，避免蓝图重建导致零件吸附原点；96 门、864 零件运行检查通过。</x:v>
-      </x:c>
-      <x:c r="E9" s="7" t="str">
-        <x:v>后续改蓝图时保留运行时挂接规则，并复核零件世界变换。</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G9" s="7" t="str">
-        <x:v>教室门交互说明：挂接策略与运行验证</x:v>
-      </x:c>
-      <x:c r="H9" s="16" t="str"/>
-    </x:row>
-    <x:row r="10" ht="75" customHeight="1">
-      <x:c r="A10" s="7" t="str">
-        <x:v>CA-012</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="str">
-        <x:v>教师楼双门同步控制蓝图</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>2—4 层 6 组双门一次 E 同步开关，每扇 90°；旧独立控制器已移除，最终 65 组、75 片门扇运行状态核对通过。</x:v>
+        <x:v>门零件在编辑器挂到根组件，BeginPlay 以 KeepWorld 快照挂到 DoorPivot，避免蓝图重建导致零件吸附原点；96 门、864 零件运行检查通过。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>以后复用双门时检查同步状态、控制器数量和双侧输入。</x:v>
+        <x:v>后续改蓝图时保留运行时挂接规则，并复核零件世界变换。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>教师楼双门 completion 与 runtime_final</x:v>
+        <x:v>教室门交互说明：挂接策略与运行验证</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
-    <x:row r="11" ht="92" customHeight="1">
+    <x:row r="11" ht="75" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>CA-013</x:v>
+        <x:v>CA-012</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>综合楼配对引用与单次按键同步逻辑</x:v>
+        <x:v>教师楼双门同步控制蓝图</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>PartnerDoor 互相引用，右扇主门接收 E 并同步状态，另一扇执行自身动画，避免一次按键重复切换；12 组运行状态及配对引用验证通过。</x:v>
+        <x:v>2—4 层 6 组双门一次 E 同步开关，每扇 90°；旧独立控制器已移除，最终 65 组、75 片门扇运行状态核对通过。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>新门组沿用单主门与互相引用规则，复查铰链和闭合状态。</x:v>
+        <x:v>以后复用双门时检查同步状态、控制器数量和双侧输入。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>综合楼双门交互说明：组控制实现</x:v>
+        <x:v>教师楼双门 completion 与 runtime_final</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
     <x:row r="12" ht="92" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>CA-017</x:v>
+        <x:v>CA-013</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>镜像实例批次生成逻辑修复</x:v>
+        <x:v>综合楼配对引用与单次按键同步逻辑</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>Content/Python/campus_editable_ism.py 已将镜像负缩放从单实例移到批次根组件，并保留原世界变换和反向剔除设置；13 项回归与 Python 语法检查通过。</x:v>
+        <x:v>PartnerDoor 互相引用，右扇主门接收 E 并同步状态，另一扇执行自身动画，避免一次按键重复切换；12 组运行状态及配对引用验证通过。</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>自动生成逻辑改动时复查负缩放实例和源构件世界变换。</x:v>
+        <x:v>新门组沿用单主门与互相引用规则，复查铰链和闭合状态。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46292</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
-        <x:v>教学楼 B 修复记录及自动实例化脚本</x:v>
+        <x:v>综合楼双门交互说明：组控制实现</x:v>
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
-    <x:row r="13" ht="75" customHeight="1">
+    <x:row r="13" ht="92" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>CA-018</x:v>
+        <x:v>CA-017</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>第一人称输入与角色蓝图接入</x:v>
+        <x:v>镜像实例批次生成逻辑修复</x:v>
       </x:c>
       <x:c r="C13" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
+        <x:v>Content/Python/campus_editable_ism.py 已将镜像负缩放从单实例移到批次根组件，并保留原世界变换和反向剔除设置；13 项回归与 Python 语法检查通过。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>自动生成逻辑改动时复查负缩放实例和源构件世界变换。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>教学楼 B 修复记录及自动实例化脚本</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="7" t="str">
+        <x:v>CA-018</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>第一人称输入与角色蓝图接入</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
         <x:v>第一人称角色蓝图已编译并接入当前校园播放配置；WASD、鼠标左右转向/上下观察、空格跳跃及落地实测通过，资产和关卡已保存。</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="str">
+      <x:c r="E14" s="7" t="str">
         <x:v>后续输入或默认角色修改后复核实际操控和出生配置。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>46290</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="str">
+      <x:c r="G14" s="7" t="str">
         <x:v>第一人称角色聊天最终结果</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="1"/>
-      <x:c r="E14" s="1"/>
-      <x:c r="F14" s="1"/>
-      <x:c r="G14" s="1"/>
-      <x:c r="H14" s="1"/>
-    </x:row>
-    <x:row r="15" ht="34" customHeight="1">
-      <x:c r="A15" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B15" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C15" s="21"/>
-      <x:c r="D15" s="21"/>
-      <x:c r="E15" s="21"/>
-      <x:c r="F15" s="21"/>
-      <x:c r="G15" s="21"/>
-      <x:c r="H15" s="21"/>
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="92" customHeight="1">
+      <x:c r="A15" s="7" t="str">
+        <x:v>CA-035</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>White 编辑器姿态自动恢复钩子</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>定位为网格姿态未刷新，位置和地面碰撞正常。最终以关卡打开及 end_pie 回调自动恢复 scene 的 30 个实例；撤回无效构造脚本，已保存，未启用持续编辑器动画 Tick。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>实现交付完成，打开关卡及退出运行的复发验收见 CA-035.02。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>White 下沉修复最终结果与两类自动回调记录</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1"/>
@@ -698,11 +722,35 @@
       <x:c r="G16" s="1"/>
       <x:c r="H16" s="1"/>
     </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B17" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C17" s="21"/>
+      <x:c r="D17" s="21"/>
+      <x:c r="E17" s="21"/>
+      <x:c r="F17" s="21"/>
+      <x:c r="G17" s="21"/>
+      <x:c r="H17" s="21"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B15:H15"/>
+    <x:mergeCell ref="B17:H17"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C13">
+  <x:conditionalFormatting sqref="C8:C15">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -714,13 +762,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C13">
+    <x:dataValidation type="list" sqref="C8:C15">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a5ddaa74514455"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9140eae1303c4ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R3a8702f4460d46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R24986e97fd794bd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-02 09:10:38（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>标准 BuildCookRun 编译和 cook 产品写出后，因 AssetManager 缺少 GameFeatureData 规则失败，UAT 退出 25。诊断包使用 skipbuild/skipcook 完成打包，不代表该配置错误已解决。</x:v>
+        <x:v>10月3日两次Shipping发布构建副本已补GameFeatureData AlwaysCook规则并成功。build_status明确build_only_changes，原工程Config/DefaultGame.ini未见该规则；原工程标准打包配置修复不能由副本成功推定。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认规则修复范围；当前聊天授权测试与方案，未实施修复。标准发布复验另见 CA-038.02。</x:v>
+        <x:v>确认是否需将副本规则同步原工程并标准复验；副本完整构建交付另见CA-038.02。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46297</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>Shipping 报告构建错误与 build_metadata exit_code=25</x:v>
+        <x:v>新发布build_status与原工程配置只读核对</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -573,46 +573,46 @@
         <x:v>CA-011</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>教室门蓝图运行时挂接与转轴逻辑</x:v>
+        <x:v>教室门原生挂接与转轴逻辑</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>门零件在编辑器挂到根组件，BeginPlay 以 KeepWorld 快照挂到 DoorPivot，避免蓝图重建导致零件吸附原点；96 门、864 零件运行检查通过。</x:v>
+        <x:v>教室门挂接、转轴与E/Y距离逻辑已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>后续改蓝图时保留运行时挂接规则，并复核零件世界变换。</x:v>
+        <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46292</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>教室门交互说明：挂接策略与运行验证</x:v>
+        <x:v>原生门迁移、重载与32项测试</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
-    <x:row r="11" ht="75" customHeight="1">
+    <x:row r="11" ht="92" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>CA-012</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>教师楼双门同步控制蓝图</x:v>
+        <x:v>教师楼原生双门同步控制</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>2—4 层 6 组双门一次 E 同步开关，每扇 90°；旧独立控制器已移除，最终 65 组、75 片门扇运行状态核对通过。</x:v>
+        <x:v>教师楼双门同步与门扇开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>以后复用双门时检查同步状态、控制器数量和双侧输入。</x:v>
+        <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
-        <x:v>46292</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>教师楼双门 completion 与 runtime_final</x:v>
+        <x:v>原生门迁移、重载与32项测试</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -621,22 +621,22 @@
         <x:v>CA-013</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>综合楼配对引用与单次按键同步逻辑</x:v>
+        <x:v>综合楼原生配对与单次输入同步</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>PartnerDoor 互相引用，右扇主门接收 E 并同步状态，另一扇执行自身动画，避免一次按键重复切换；12 组运行状态及配对引用验证通过。</x:v>
+        <x:v>综合楼配对及同次按键开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>新门组沿用单主门与互相引用规则，复查铰链和闭合状态。</x:v>
+        <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="n">
-        <x:v>46292</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
-        <x:v>综合楼双门交互说明：组控制实现</x:v>
+        <x:v>原生门迁移、重载与32项测试</x:v>
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
@@ -664,27 +664,27 @@
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
-    <x:row r="14" ht="75" customHeight="1">
+    <x:row r="14" ht="92" customHeight="1">
       <x:c r="A14" s="7" t="str">
         <x:v>CA-018</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>第一人称输入与角色蓝图接入</x:v>
+        <x:v>人物原生输入与角色控制接入</x:v>
       </x:c>
       <x:c r="C14" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>第一人称角色蓝图已编译并接入当前校园播放配置；WASD、鼠标左右转向/上下观察、空格跳跃及落地实测通过，资产和关卡已保存。</x:v>
+        <x:v>第一/第三人称输入、相机及触摸调用链已迁入C++，第一和第三人称输入各16项、第一人称/触摸9项通过。人物配置资产保留；最新scene入口另改为无网格观察摄像机。</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>后续输入或默认角色修改后复核实际操控和出生配置。</x:v>
+        <x:v>原人物控制阶段验收有效；当前scene玩法入口见CA-054，手柄适用性见CA-045.05。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="n">
-        <x:v>46290</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>第一人称角色聊天最终结果</x:v>
+        <x:v>C++人物控制迁移与最新观察入口</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
@@ -768,7 +768,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9140eae1303c4ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ce03a4876f4dd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R24986e97fd794bd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="Rcac4b23a2e6a4706"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H19"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,A5)</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIF(C8:C19,A5)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,D5)</x:f>
+        <x:f>COUNTIF(C8:C19,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,F5)</x:f>
-        <x:v>2</x:v>
+        <x:f>COUNTIF(C8:C19,F5)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -544,42 +544,42 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="109" customHeight="1">
+    <x:row r="9" ht="92" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>CA-038</x:v>
+        <x:v>CA-011</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>标准 Shipping 打包 GameFeatureData 规则错误</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>待确认</x:v>
+        <x:v>教室门原生挂接与转轴逻辑</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>10月3日两次Shipping发布构建副本已补GameFeatureData AlwaysCook规则并成功。build_status明确build_only_changes，原工程Config/DefaultGame.ini未见该规则；原工程标准打包配置修复不能由副本成功推定。</x:v>
+        <x:v>教室门挂接、转轴与E/Y距离逻辑已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认是否需将副本规则同步原工程并标准复验；副本完整构建交付另见CA-038.02。</x:v>
+        <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>新发布build_status与原工程配置只读核对</x:v>
+        <x:v>原生门迁移、重载与32项测试</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
     <x:row r="10" ht="92" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>CA-011</x:v>
+        <x:v>CA-012</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>教室门原生挂接与转轴逻辑</x:v>
+        <x:v>教师楼原生双门同步控制</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>教室门挂接、转轴与E/Y距离逻辑已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
+        <x:v>教师楼双门同步与门扇开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
@@ -594,16 +594,16 @@
     </x:row>
     <x:row r="11" ht="92" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>CA-012</x:v>
+        <x:v>CA-013</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>教师楼原生双门同步控制</x:v>
+        <x:v>综合楼原生配对与单次输入同步</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>教师楼双门同步与门扇开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
+        <x:v>综合楼配对及同次按键开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
@@ -618,139 +618,235 @@
     </x:row>
     <x:row r="12" ht="92" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>CA-013</x:v>
+        <x:v>CA-017</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>综合楼原生配对与单次输入同步</x:v>
+        <x:v>镜像实例批次生成逻辑修复</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>综合楼配对及同次按键开关已从业务蓝图迁入C++门类，配置蓝图及场景引用保留。保存重开963挂接零件与实例参数一致，四类门32项开关/距离/联动检查通过。</x:v>
+        <x:v>Content/Python/campus_editable_ism.py 已将镜像负缩放从单实例移到批次根组件，并保留原世界变换和反向剔除设置；13 项回归与 Python 语法检查通过。</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
+        <x:v>自动生成逻辑改动时复查负缩放实例和源构件世界变换。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46291</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
-        <x:v>原生门迁移、重载与32项测试</x:v>
+        <x:v>教学楼 B 修复记录及自动实例化脚本</x:v>
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
-    <x:row r="13" ht="92" customHeight="1">
+    <x:row r="13" ht="109" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>CA-017</x:v>
+        <x:v>CA-018</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>镜像实例批次生成逻辑修复</x:v>
+        <x:v>人物原生输入与角色控制接入</x:v>
       </x:c>
       <x:c r="C13" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>Content/Python/campus_editable_ism.py 已将镜像负缩放从单实例移到批次根组件，并保留原世界变换和反向剔除设置；13 项回归与 Python 语法检查通过。</x:v>
+        <x:v>第一/第三人称输入和相机已迁入C++，旧阶段各16项输入测试保留。用户10月4日明确选择启动默认第一人称，scene入口已恢复BP_FirstPersonCharacter，15项出生、控制、碰撞移动和跳跃检查通过。</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>自动生成逻辑改动时复查负缩放实例和源构件世界变换。</x:v>
+        <x:v>当前第一人称入口以10月4日修订为准；新入口验收见CA-055，实体手柄范围见CA-045.05。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>教学楼 B 修复记录及自动实例化脚本</x:v>
+        <x:v>用户直接选择与第一人称15项运行验收</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
     <x:row r="14" ht="92" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>CA-018</x:v>
+        <x:v>CA-035</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>人物原生输入与角色控制接入</x:v>
+        <x:v>White 编辑器姿态自动恢复钩子</x:v>
       </x:c>
       <x:c r="C14" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>第一/第三人称输入、相机及触摸调用链已迁入C++，第一和第三人称输入各16项、第一人称/触摸9项通过。人物配置资产保留；最新scene入口另改为无网格观察摄像机。</x:v>
+        <x:v>定位为网格姿态未刷新，位置和地面碰撞正常。最终以关卡打开及 end_pie 回调自动恢复 scene 的 30 个实例；撤回无效构造脚本，已保存，未启用持续编辑器动画 Tick。</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>原人物控制阶段验收有效；当前scene玩法入口见CA-054，手柄适用性见CA-045.05。</x:v>
+        <x:v>实现交付完成，打开关卡及退出运行的复发验收见 CA-035.02。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>C++人物控制迁移与最新观察入口</x:v>
+        <x:v>White 下沉修复最终结果与两类自动回调记录</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
-    <x:row r="15" ht="92" customHeight="1">
+    <x:row r="15" ht="109" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>CA-035</x:v>
+        <x:v>CA-038</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>White 编辑器姿态自动恢复钩子</x:v>
+        <x:v>标准 Shipping 打包 GameFeatureData 规则错误</x:v>
       </x:c>
       <x:c r="C15" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>定位为网格姿态未刷新，位置和地面碰撞正常。最终以关卡打开及 end_pie 回调自动恢复 scene 的 30 个实例；撤回无效构造脚本，已保存，未启用持续编辑器动画 Tick。</x:v>
+        <x:v>原工程DefaultGame.ini已加入GameFeatureData AlwaysCook规则。10月4日build_project和source_project均为原工程，完整build/cook/stage/package退出0，full_cook=true；10月5日一键脚本再次构建成功。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>实现交付完成，打开关卡及退出运行的复发验收见 CA-035.02。</x:v>
+        <x:v>原工程规则缺口已关闭；最新白天修订发布同步见CA-046.03。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>46296</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>White 下沉修复最终结果与两类自动回调记录</x:v>
+        <x:v>原工程配置与两次完整Shipping成功记录</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="1"/>
-      <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1"/>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-    </x:row>
-    <x:row r="17" ht="34" customHeight="1">
-      <x:c r="A17" s="3" t="str">
+    <x:row r="16" ht="92" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>CA-064</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>十分钟昼夜时钟与控制器保存</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>C++控制器已保存scene，600秒一天、早8点开始，动态太阳、曝光和雾；20Hz环境更新，灯具初始化扫描，不逐帧遍历或循环RecaptureSky。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>昼夜以当前使用说明与白天修订为准。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>使用说明与控制器保存</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="75" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>CA-064.02</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>白天全关灯与日落后启灯规则</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>按用户纠正，06:00–18:00所有300受控灯强制关闭，18:03后错峰渐亮；礼堂6灯亦纳入，旧Ignore标签不豁免。正午零灯检查passed。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>夜晚亮度基准与还原验收见CA-064.07；过时294室外灯仅为初版样本。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>用户白天禁灯纠正与scene_blackout</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="92" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>CA-065</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>scene一键完整Shipping打包脚本</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>PackageScene.bat与Scripts/PackageScene.ps1已交付，自动识别引擎、完整build/cook、scene地图、独立输出与日志，成功文件检查；路径及模拟成功/失败测试通过。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>真实构建结果另见CA-065.03，不执行脚本替代追踪。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>打包脚本聊天与使用说明</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="92" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>CA-065.02</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>一键打包等待编辑器退出修订</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>用户反馈编辑器打开阻止打包后，入口改为WaitForEditor：等待用户保存并关闭后继续。独立调用无等待默认仍保护退出，修订已验证。</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>等待时保留脚本窗口，错误或中断不认定成品。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>用户错误反馈与最终脚本修订</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1"/>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1"/>
+      <x:c r="H20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B17" s="21" t="str">
+      <x:c r="B21" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C17" s="21"/>
-      <x:c r="D17" s="21"/>
-      <x:c r="E17" s="21"/>
-      <x:c r="F17" s="21"/>
-      <x:c r="G17" s="21"/>
-      <x:c r="H17" s="21"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
+      <x:c r="C21" s="21"/>
+      <x:c r="D21" s="21"/>
+      <x:c r="E21" s="21"/>
+      <x:c r="F21" s="21"/>
+      <x:c r="G21" s="21"/>
+      <x:c r="H21" s="21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B17:H17"/>
+    <x:mergeCell ref="B21:H21"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C15">
+  <x:conditionalFormatting sqref="C8:C19">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -762,13 +858,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C15">
+    <x:dataValidation type="list" sqref="C8:C19">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ce03a4876f4dd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recf2f7d248274ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="Rcac4b23a2e6a4706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R85dc9a5d0fcc4858"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H21"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
+        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C19,A5)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIF(C8:C21,A5)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C19,D5)</x:f>
+        <x:f>COUNTIF(C8:C21,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C19,F5)</x:f>
+        <x:f>COUNTIF(C8:C21,F5)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -736,27 +736,27 @@
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="75" customHeight="1">
+    <x:row r="17" ht="109" customHeight="1">
       <x:c r="A17" s="7" t="str">
         <x:v>CA-064.02</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>白天全关灯与日落后启灯规则</x:v>
+        <x:v>日间关灯与黄昏提前渐亮规则</x:v>
       </x:c>
       <x:c r="C17" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>按用户纠正，06:00–18:00所有300受控灯强制关闭，18:03后错峰渐亮；礼堂6灯亦纳入，旧Ignore标签不豁免。正午零灯检查passed。</x:v>
+        <x:v>10月5日最新用户要求在日落前慢慢开灯，替代旧06–18禁灯阶段。已保存17:00开始分批渐亮、19:15左右全亮；600秒一天对应约56秒过渡。17:30启动187灯、18:00启动300灯，启动数不等于已达全亮。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>夜晚亮度基准与还原验收见CA-064.07；过时294室外灯仅为初版样本。</x:v>
+        <x:v>当前以17:00提前开灯规则为准；旧18:03规则仅保留阶段依据。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>用户白天禁灯纠正与scene_blackout</x:v>
+        <x:v>最新用户开灯需求及300灯场景检查</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
@@ -808,29 +808,53 @@
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="1"/>
-      <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-      <x:c r="E20" s="1"/>
-      <x:c r="F20" s="1"/>
-      <x:c r="G20" s="1"/>
-      <x:c r="H20" s="1"/>
-    </x:row>
-    <x:row r="21" ht="34" customHeight="1">
-      <x:c r="A21" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B21" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C21" s="21"/>
-      <x:c r="D21" s="21"/>
-      <x:c r="E21" s="21"/>
-      <x:c r="F21" s="21"/>
-      <x:c r="G21" s="21"/>
-      <x:c r="H21" s="21"/>
+    <x:row r="20" ht="75" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-066</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>编辑器时间预览面板接入</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>原生Slate时间面板已停靠右侧，支持滑条、时分输入、快捷时段、自动播放暂停和恢复原夜景；无需PIE即可实时预览。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>入口为顶部时间或窗口时间预览；运行从8点开始的规则保留。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>时间面板最终交付及原生控件检查</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="75" customHeight="1">
+      <x:c r="A21" s="7" t="str">
+        <x:v>CA-068</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>月亮月光共轨与升落时序</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>月亮约18:00升起、午夜达到55度最高点、06:00落下；月光与月盘共享轨道和可见性逻辑，已编译保存。</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>日落前启灯规则独立见CA-064.02。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>月亮最终交付及轨道检查</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1"/>
@@ -842,11 +866,35 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
     </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B23" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C23" s="21"/>
+      <x:c r="D23" s="21"/>
+      <x:c r="E23" s="21"/>
+      <x:c r="F23" s="21"/>
+      <x:c r="G23" s="21"/>
+      <x:c r="H23" s="21"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B21:H21"/>
+    <x:mergeCell ref="B23:H23"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C19">
+  <x:conditionalFormatting sqref="C8:C21">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -858,13 +906,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C19">
+    <x:dataValidation type="list" sqref="C8:C21">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recf2f7d248274ef4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R768ce45192f44c9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R85dc9a5d0fcc4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R918be0438eda4be5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H25"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,A5)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF(C8:C25,A5)</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,D5)</x:f>
+        <x:f>COUNTIF(C8:C25,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,F5)</x:f>
+        <x:f>COUNTIF(C8:C25,F5)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -856,45 +856,141 @@
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="1"/>
-      <x:c r="B22" s="1"/>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-    </x:row>
-    <x:row r="23" ht="34" customHeight="1">
-      <x:c r="A23" s="3" t="str">
+    <x:row r="22" ht="75" customHeight="1">
+      <x:c r="A22" s="7" t="str">
+        <x:v>CA-072.03</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>150人人群容量与错峰首次寻路</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>DetourCrowd容量从128提升至256，150名学生首次寻路错开约8秒；保留全校园目标、避让、体力、休息和自然动画逻辑，编译成功。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>行为运行结果见CA-072.04；座位限制独立见CA-072.05。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>原生编译、容量与全部控制器检查</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="109" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-073</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>随机阴雨调度与三十秒渐变</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>最新用户要求天气有过渡且30分钟至少变化一次。实现按现实游玩时间随机600–1800秒切换阴天或下雨，上限1800秒，默认30秒连续渐变，可从中途当前状态改选另一种天气；scene保存。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>旧90–180/70–140秒及12秒过渡仅为初版；时间口径采用聊天实现的现实游玩时间。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>用户后续需求、配置保存与24项测试</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="92" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-073.02</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>跟随观察位置的雨滴与屋顶遮挡</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>雨丝跟随观察位置，使用屋顶与地面碰撞检查，停止降雨时清除可见雨滴；宽屋顶内0雨滴、室外雨滴及地面上方留空验证通过，遮挡检测每tick上限8条。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>检查覆盖宽屋顶与地面；不扩大为所有窄屋檐边缘精度验收。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>屋顶与地面304帧验证</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="92" customHeight="1">
+      <x:c r="A25" s="7" t="str">
+        <x:v>CA-073.06</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>时间与天气面板手动渐变按钮</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>现有时间面板扩展阴天/下雨按钮、当前雨量与过渡进度；详情天气按钮误改时间的问题已修正，面板按钮与详情触发均从当前视觉状态开始过渡。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>原时间滑条功能见CA-066；实际点击验收见CA-073.09。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>天气面板交付与编译测试</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B23" s="21" t="str">
+      <x:c r="B27" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C23" s="21"/>
-      <x:c r="D23" s="21"/>
-      <x:c r="E23" s="21"/>
-      <x:c r="F23" s="21"/>
-      <x:c r="G23" s="21"/>
-      <x:c r="H23" s="21"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
+      <x:c r="C27" s="21"/>
+      <x:c r="D27" s="21"/>
+      <x:c r="E27" s="21"/>
+      <x:c r="F27" s="21"/>
+      <x:c r="G27" s="21"/>
+      <x:c r="H27" s="21"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B23:H23"/>
+    <x:mergeCell ref="B27:H27"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C21">
+  <x:conditionalFormatting sqref="C8:C25">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -906,13 +1002,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C21">
+    <x:dataValidation type="list" sqref="C8:C25">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R768ce45192f44c9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72c55d20a4fe4329"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R918be0438eda4be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R465f0b7fbf2e4c51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -192,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H27"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +470,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,A5)</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTIF(C8:C27,A5)</x:f>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,D5)</x:f>
+        <x:f>COUNTIF(C8:C27,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,F5)</x:f>
+        <x:f>COUNTIF(C8:C27,F5)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -536,8 +542,8 @@
       <x:c r="E8" s="7" t="str">
         <x:v>确认仍需复用哪些历史脚本，逐个核对资产路径后再运行。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>46293</x:v>
+      <x:c r="F8" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
         <x:v>Content 整理报告：历史脚本适用范围</x:v>
@@ -560,8 +566,8 @@
       <x:c r="E9" s="7" t="str">
         <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F9" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>原生门迁移、重载与32项测试</x:v>
@@ -584,8 +590,8 @@
       <x:c r="E10" s="7" t="str">
         <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F10" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>原生门迁移、重载与32项测试</x:v>
@@ -608,8 +614,8 @@
       <x:c r="E11" s="7" t="str">
         <x:v>保留当前原生实现与配置资源；全校逐门覆盖缺口见CA-010。</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F11" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
         <x:v>原生门迁移、重载与32项测试</x:v>
@@ -632,8 +638,8 @@
       <x:c r="E12" s="7" t="str">
         <x:v>自动生成逻辑改动时复查负缩放实例和源构件世界变换。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
-        <x:v>46291</x:v>
+      <x:c r="F12" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>教学楼 B 修复记录及自动实例化脚本</x:v>
@@ -656,8 +662,8 @@
       <x:c r="E13" s="7" t="str">
         <x:v>当前第一人称入口以10月4日修订为准；新入口验收见CA-055，实体手柄范围见CA-045.05。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F13" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>用户直接选择与第一人称15项运行验收</x:v>
@@ -680,8 +686,8 @@
       <x:c r="E14" s="7" t="str">
         <x:v>实现交付完成，打开关卡及退出运行的复发验收见 CA-035.02。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46296</x:v>
+      <x:c r="F14" s="14" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>White 下沉修复最终结果与两类自动回调记录</x:v>
@@ -704,8 +710,8 @@
       <x:c r="E15" s="7" t="str">
         <x:v>原工程规则缺口已关闭；最新白天修订发布同步见CA-046.03。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F15" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
         <x:v>原工程配置与两次完整Shipping成功记录</x:v>
@@ -728,8 +734,8 @@
       <x:c r="E16" s="7" t="str">
         <x:v>昼夜以当前使用说明与白天修订为准。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F16" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>使用说明与控制器保存</x:v>
@@ -752,8 +758,8 @@
       <x:c r="E17" s="7" t="str">
         <x:v>当前以17:00提前开灯规则为准；旧18:03规则仅保留阶段依据。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F17" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>最新用户开灯需求及300灯场景检查</x:v>
@@ -776,8 +782,8 @@
       <x:c r="E18" s="7" t="str">
         <x:v>真实构建结果另见CA-065.03，不执行脚本替代追踪。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
         <x:v>打包脚本聊天与使用说明</x:v>
@@ -800,8 +806,8 @@
       <x:c r="E19" s="7" t="str">
         <x:v>等待时保留脚本窗口，错误或中断不认定成品。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F19" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
         <x:v>用户错误反馈与最终脚本修订</x:v>
@@ -824,8 +830,8 @@
       <x:c r="E20" s="7" t="str">
         <x:v>入口为顶部时间或窗口时间预览；运行从8点开始的规则保留。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F20" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>时间面板最终交付及原生控件检查</x:v>
@@ -848,8 +854,8 @@
       <x:c r="E21" s="7" t="str">
         <x:v>日落前启灯规则独立见CA-064.02。</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F21" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>月亮最终交付及轨道检查</x:v>
@@ -872,35 +878,35 @@
       <x:c r="E22" s="7" t="str">
         <x:v>行为运行结果见CA-072.04；座位限制独立见CA-072.05。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F22" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
         <x:v>原生编译、容量与全部控制器检查</x:v>
       </x:c>
       <x:c r="H22" s="16" t="str"/>
     </x:row>
-    <x:row r="23" ht="109" customHeight="1">
+    <x:row r="23" ht="92" customHeight="1">
       <x:c r="A23" s="7" t="str">
         <x:v>CA-073</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>随机阴雨调度与三十秒渐变</x:v>
+        <x:v>随机晴雨调度与三十秒渐变</x:v>
       </x:c>
       <x:c r="C23" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>最新用户要求天气有过渡且30分钟至少变化一次。实现按现实游玩时间随机600–1800秒切换阴天或下雨，上限1800秒，默认30秒连续渐变，可从中途当前状态改选另一种天气；scene保存。</x:v>
+        <x:v>按最新用户纠正，非雨端由阴天改为晴天，旧Overcast序列化值迁移为Clear；现实游玩时间600–1800秒切换晴天/下雨、30秒渐变，切换不改变当前时间，scene保存。</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>旧90–180/70–140秒及12秒过渡仅为初版；时间口径采用聊天实现的现实游玩时间。</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>10月6日阴雨版保留历史依据；当前晴雨以10月8日纠正为准，旧时长上限要求保持。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>用户后续需求、配置保存与24项测试</x:v>
+        <x:v>晴空直接纠正、场景保存、调度源码与27项测试</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
@@ -920,8 +926,8 @@
       <x:c r="E24" s="7" t="str">
         <x:v>检查覆盖宽屋顶与地面；不扩大为所有窄屋檐边缘精度验收。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
         <x:v>屋顶与地面304帧验证</x:v>
@@ -939,42 +945,66 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>现有时间面板扩展阴天/下雨按钮、当前雨量与过渡进度；详情天气按钮误改时间的问题已修正，面板按钮与详情触发均从当前视觉状态开始过渡。</x:v>
+        <x:v>编辑器时间天气面板改为“渐变到晴天 / 渐变到下雨”，保留雨量和过渡状态；旧阴天按钮被替代。实际面板与四组合预览确认，切天气不改变时间。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
         <x:v>原时间滑条功能见CA-066；实际点击验收见CA-073.09。</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F25" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>天气面板交付与编译测试</x:v>
+        <x:v>最新按钮命名纠正与面板场景确认</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-    </x:row>
-    <x:row r="27" ht="34" customHeight="1">
-      <x:c r="A27" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B27" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C27" s="21"/>
-      <x:c r="D27" s="21"/>
-      <x:c r="E27" s="21"/>
-      <x:c r="F27" s="21"/>
-      <x:c r="G27" s="21"/>
-      <x:c r="H27" s="21"/>
+    <x:row r="26" ht="75" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-074.02</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>灯光回路多点联动与手动状态保持</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>原生回路逻辑、多个面板共享状态和手动覆盖已实现并编译通过；161回路逐一开关检查通过，昼夜变化保持行为有自动化依据。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>场景运行回路检查见CA-074.06；雨天联动的后续修正见CA-075.04。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>编译、161回路运行与原生测试</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="75" customHeight="1">
+      <x:c r="A27" s="7" t="str">
+        <x:v>CA-075.04</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>雨天中午亮灯与手动开关状态一致</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>修正雨天中午灯已亮但开关仍判断关闭的问题，天气亮灯、手动切换及恢复纳入26项天气昼夜灯光测试，全部通过。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>最终晴空恢复后27项回归见CA-073.08。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>雨景用户聊天实施与26项0失败</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1"/>
@@ -986,11 +1016,35 @@
       <x:c r="G28" s="1"/>
       <x:c r="H28" s="1"/>
     </x:row>
+    <x:row r="29" ht="34" customHeight="1">
+      <x:c r="A29" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B29" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C29" s="21"/>
+      <x:c r="D29" s="21"/>
+      <x:c r="E29" s="21"/>
+      <x:c r="F29" s="21"/>
+      <x:c r="G29" s="21"/>
+      <x:c r="H29" s="21"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B27:H27"/>
+    <x:mergeCell ref="B29:H29"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C25">
+  <x:conditionalFormatting sqref="C8:C27">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1002,13 +1056,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C25">
+    <x:dataValidation type="list" sqref="C8:C27">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72c55d20a4fe4329"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0fe320861534cea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/代码问题.xlsx
+++ b/ProjectProgress/表格/分类进展/代码问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R465f0b7fbf2e4c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="代码问题" sheetId="1" r:id="R746bc01496494428"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress6" displayName="CategoryProgress6" ref="A7:H28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H28"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -470,22 +470,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,A5)</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTIF(C8:C28,A5)</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,D5)</x:f>
+        <x:f>COUNTIF(C8:C28,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,F5)</x:f>
+        <x:f>COUNTIF(C8:C28,F5)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -742,7 +742,7 @@
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="109" customHeight="1">
+    <x:row r="17" ht="92" customHeight="1">
       <x:c r="A17" s="7" t="str">
         <x:v>CA-064.02</x:v>
       </x:c>
@@ -753,16 +753,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>10月5日最新用户要求在日落前慢慢开灯，替代旧06–18禁灯阶段。已保存17:00开始分批渐亮、19:15左右全亮；600秒一天对应约56秒过渡。17:30启动187灯、18:00启动300灯，启动数不等于已达全亮。</x:v>
+        <x:v>17:00分批渐亮、19:15左右全亮的黄昏阶段交付保留。10月9日用户要求墙壁开关区域默认关闭后，这些室内回路不会随昼夜或雨天自动重开；非手动回路保留黄昏规则。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>当前以17:00提前开灯规则为准；旧18:03规则仅保留阶段依据。</x:v>
+        <x:v>受控室内灯遵循CA-074.02；旧300灯与56秒过渡为历史验收范围，不能将当前所有室内灯视作夜间自动亮起。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>最新用户开灯需求及300灯场景检查</x:v>
+        <x:v>黄昏阶段交付及最新室内默认关闭要求</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
@@ -958,93 +958,117 @@
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
-    <x:row r="26" ht="75" customHeight="1">
+    <x:row r="26" ht="92" customHeight="1">
       <x:c r="A26" s="7" t="str">
         <x:v>CA-074.02</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>灯光回路多点联动与手动状态保持</x:v>
+        <x:v>多点灯光回路默认关闭与手动状态保持</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>原生回路逻辑、多个面板共享状态和手动覆盖已实现并编译通过；161回路逐一开关检查通过，昼夜变化保持行为有自动化依据。</x:v>
+        <x:v>按用户最新要求，五栋楼受控回路默认关闭，昼夜和雨天不会自动重开；前后面板共享状态。3项原生初始化顺序、时钟雨天默认关闭、联动昼夜测试通过。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>场景运行回路检查见CA-074.06；雨天联动的后续修正见CA-075.04。</x:v>
+        <x:v>该规则优先作用于墙壁开关受控灯具；室外非手动回路的黄昏渐亮仍按CA-064.02。教室后续联动见CA-079.04。</x:v>
       </x:c>
       <x:c r="F26" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>编译、161回路运行与原生测试</x:v>
+        <x:v>最新默认关闭要求、3项原生测试与保存交付</x:v>
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
-    <x:row r="27" ht="75" customHeight="1">
+    <x:row r="27" ht="92" customHeight="1">
       <x:c r="A27" s="7" t="str">
         <x:v>CA-075.04</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>雨天中午亮灯与手动开关状态一致</x:v>
+        <x:v>雨天受控室内灯手动状态一致</x:v>
       </x:c>
       <x:c r="C27" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>修正雨天中午灯已亮但开关仍判断关闭的问题，天气亮灯、手动切换及恢复纳入26项天气昼夜灯光测试，全部通过。</x:v>
+        <x:v>10月8日修正雨天中午灯已亮但面板判断关闭的阶段保留。最新用户要求默认关闭后，受控室内灯不再因雨天自动重开；3项默认关闭和联动昼夜原生回归通过。</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>最终晴空恢复后27项回归见CA-073.08。</x:v>
+        <x:v>当前手动开关优先规则见CA-074.02；旧26/27项天气结果保留历史，不作为新默认关闭策略全部重测依据。</x:v>
       </x:c>
       <x:c r="F27" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>雨景用户聊天实施与26项0失败</x:v>
+        <x:v>默认关闭直接要求与新原生回归</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="1"/>
-      <x:c r="B28" s="1"/>
-      <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
-      <x:c r="H28" s="1"/>
-    </x:row>
-    <x:row r="29" ht="34" customHeight="1">
-      <x:c r="A29" s="3" t="str">
+    <x:row r="28" ht="92" customHeight="1">
+      <x:c r="A28" s="7" t="str">
+        <x:v>CA-077</x:v>
+      </x:c>
+      <x:c r="B28" s="7" t="str">
+        <x:v>DualSense与Edge原生设备接入配置</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
+        <x:v>GameInputWindows接入DualSense/Edge两个设备标识，保留XInput的Xbox路径，配置回读、插件加载及GameInput初始化检查通过；配置和操作说明已保存。</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>原编辑器需要重启；硬件实测见CA-077.03，包构建时序见CA-046.08。未授权增加专用触觉或自适应扳机。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>validation-final八检查通过</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="1"/>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="34" customHeight="1">
+      <x:c r="A30" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B29" s="21" t="str">
+      <x:c r="B30" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C29" s="21"/>
-      <x:c r="D29" s="21"/>
-      <x:c r="E29" s="21"/>
-      <x:c r="F29" s="21"/>
-      <x:c r="G29" s="21"/>
-      <x:c r="H29" s="21"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="1"/>
-      <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-      <x:c r="H30" s="1"/>
+      <x:c r="C30" s="21"/>
+      <x:c r="D30" s="21"/>
+      <x:c r="E30" s="21"/>
+      <x:c r="F30" s="21"/>
+      <x:c r="G30" s="21"/>
+      <x:c r="H30" s="21"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
+      <x:c r="H31" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B29:H29"/>
+    <x:mergeCell ref="B30:H30"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C27">
+  <x:conditionalFormatting sqref="C8:C28">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1056,13 +1080,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C27">
+    <x:dataValidation type="list" sqref="C8:C28">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0fe320861534cea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e7693fc51ce4923"/>
   </x:tableParts>
 </x:worksheet>
 </file>